--- a/data/Creatine/lanhers2017/lanhers2017_creatine_chest_strength.xlsx
+++ b/data/Creatine/lanhers2017/lanhers2017_creatine_chest_strength.xlsx
@@ -86,7 +86,7 @@
     <t>Strength</t>
   </si>
   <si>
-    <t>n not available, smd used</t>
+    <t>n not available, d used</t>
   </si>
   <si>
     <t>Bemben</t>
